--- a/vse-loti/339522869/spec-339522869.xlsx
+++ b/vse-loti/339522869/spec-339522869.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -497,13 +497,171 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Труба 219х8 08Х18Н10Т МКК ГОСТ 9940</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34337.41</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41204.9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>434368.27</v>
+      </c>
+      <c r="I2" t="n">
+        <v>824823.75</v>
+      </c>
+      <c r="J2" t="n">
+        <v>989788.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Труба 273х8 08Х18Н10Т МКК ГОСТ 9941-2022</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>172.25</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>9.005000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>34337.41</v>
+      </c>
+      <c r="G3" t="n">
+        <v>41204.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5914619.35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>656798.25</v>
+      </c>
+      <c r="J3" t="n">
+        <v>788157.91</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Труба 273х9 10Х17Н13М2Т МКК ГОСТ 9940</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="F4" t="n">
+        <v>34337.41</v>
+      </c>
+      <c r="G4" t="n">
+        <v>41204.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>290494.51</v>
+      </c>
+      <c r="I4" t="n">
+        <v>656798.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>788157.91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Труба 32Х4 10Х17Н13М2Т МКК ГОСТ 9941</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>34337.41</v>
+      </c>
+      <c r="G5" t="n">
+        <v>41204.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7554.23</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
+      <c r="E6" s="2" t="n">
+        <v>9.974</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>6647036.36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>6647036.36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Источник: 852839668.txt</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/vse-loti/339522869/spec-339522869.xlsx
+++ b/vse-loti/339522869/spec-339522869.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +441,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,7 +512,7 @@
           <t>Труба 219х8 08Х18Н10Т МКК ГОСТ 9940</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>12.65</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,22 +520,22 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>0.527</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>34337.41</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>41204.9</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>434368.27</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>824823.75</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>989788.5</v>
       </c>
     </row>
@@ -541,7 +548,7 @@
           <t>Труба 273х8 08Х18Н10Т МКК ГОСТ 9941-2022</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>172.25</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,22 +556,22 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>9.005000000000001</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>34337.41</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>41204.9</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>5914619.35</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>656798.25</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>788157.91</v>
       </c>
     </row>
@@ -577,7 +584,7 @@
           <t>Труба 273х9 10Х17Н13М2Т МКК ГОСТ 9940</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>8.460000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -585,22 +592,22 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>0.442</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>34337.41</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>41204.9</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>290494.51</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>656798.25</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3" t="n">
         <v>788157.91</v>
       </c>
     </row>
@@ -613,7 +620,7 @@
           <t>Труба 32Х4 10Х17Н13М2Т МКК ГОСТ 9941</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -622,38 +629,38 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>34337.41</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>41204.9</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>7554.23</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="5" t="n">
         <v>9.974</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="6" t="n">
         <v>6647036.36</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="6" t="n">
         <v>6647036.36</v>
       </c>
     </row>

--- a/vse-loti/339522869/spec-339522869.xlsx
+++ b/vse-loti/339522869/spec-339522869.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -524,19 +524,19 @@
         <v>0.527</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>34337.41</v>
+        <v>30549.85</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>41204.9</v>
+        <v>36659.82</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>434368.27</v>
+        <v>386455.6</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>824823.75</v>
+        <v>733842.1800000001</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>989788.5</v>
+        <v>880610.62</v>
       </c>
     </row>
     <row r="3">
@@ -560,19 +560,19 @@
         <v>9.005000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>34337.41</v>
+        <v>30549.85</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>41204.9</v>
+        <v>36659.82</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5914619.35</v>
+        <v>5262211.66</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>656798.25</v>
+        <v>584350.61</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>788157.91</v>
+        <v>701220.73</v>
       </c>
     </row>
     <row r="4">
@@ -596,19 +596,19 @@
         <v>0.442</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>34337.41</v>
+        <v>30549.85</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>41204.9</v>
+        <v>36659.82</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>290494.51</v>
+        <v>258451.73</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>656798.25</v>
+        <v>584350.61</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>788157.91</v>
+        <v>701220.73</v>
       </c>
     </row>
     <row r="5">
@@ -630,42 +630,180 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>34337.41</v>
+        <v>30549.85</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>41204.9</v>
+        <v>36659.82</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7554.23</v>
+        <v>6720.97</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Труба 219х8 08Х18Н10Т МКК ГОСТ 9940 12,650</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>30549.85</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>36659.82</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>183299.1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>733842.1800000001</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>880610.62</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Труба 273х8 08Х18Н10Т МКК ГОСТ 9941-2022 172,250</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>30549.85</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>36659.82</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>183299.1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>584350.61</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>701220.73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Труба 273х9 10Х17Н13М2Т МКК ГОСТ 9940 8,460</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>30549.85</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>36659.82</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>183299.1</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>584350.61</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>701220.73</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Труба 32Х4 10Х17Н13М2Т МКК ГОСТ 9941 0,220</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" s="3" t="n">
+        <v>30549.85</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>36659.82</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>183299.1</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>9.974</v>
-      </c>
-      <c r="H6" s="6" t="n">
+      <c r="E10" s="5" t="n">
+        <v>10.852</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>6647036.36</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>6647036.36</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Источник: 852839668.txt</t>
         </is>

--- a/vse-loti/339522869/spec-339522869.xlsx
+++ b/vse-loti/339522869/spec-339522869.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -61,16 +62,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -447,8 +450,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +480,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -520,22 +511,16 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.527</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>30549.85</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>36659.82</v>
-      </c>
-      <c r="H2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>386455.6</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>733842.1800000001</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>880610.62</v>
       </c>
     </row>
@@ -556,22 +541,16 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>9.005000000000001</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>30549.85</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>36659.82</v>
-      </c>
-      <c r="H3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>5262211.66</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="G3" s="4" t="n">
         <v>584350.61</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>701220.73</v>
       </c>
     </row>
@@ -592,23 +571,17 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>30549.85</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>36659.82</v>
-      </c>
-      <c r="H4" s="3" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>258451.73</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>584350.61</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>701220.73</v>
+      <c r="G4" s="4" t="n">
+        <v>518066.27</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>621679.53</v>
       </c>
     </row>
     <row r="5">
@@ -629,17 +602,11 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" s="3" t="n">
-        <v>30549.85</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>36659.82</v>
-      </c>
-      <c r="H5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>6720.97</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -650,7 +617,7 @@
           <t>Труба 219х8 08Х18Н10Т МКК ГОСТ 9940 12,650</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -658,22 +625,16 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>30549.85</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>36659.82</v>
-      </c>
-      <c r="H6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>183299.1</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>733842.1800000001</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>880610.62</v>
       </c>
     </row>
@@ -686,7 +647,7 @@
           <t>Труба 273х8 08Х18Н10Т МКК ГОСТ 9941-2022 172,250</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -694,22 +655,16 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.314</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>30549.85</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>36659.82</v>
-      </c>
-      <c r="H7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>183299.1</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>584350.61</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>701220.73</v>
       </c>
     </row>
@@ -722,7 +677,7 @@
           <t>Труба 273х9 10Х17Н13М2Т МКК ГОСТ 9940 8,460</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -730,23 +685,17 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>30549.85</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>36659.82</v>
-      </c>
-      <c r="H8" s="3" t="n">
+      <c r="E8" s="3" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>183299.1</v>
       </c>
-      <c r="I8" s="3" t="n">
-        <v>584350.61</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>701220.73</v>
+      <c r="G8" s="4" t="n">
+        <v>518066.27</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>621679.53</v>
       </c>
     </row>
     <row r="9">
@@ -758,7 +707,7 @@
           <t>Труба 32Х4 10Х17Н13М2Т МКК ГОСТ 9941 0,220</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -767,38 +716,32 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" s="3" t="n">
-        <v>30549.85</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>36659.82</v>
-      </c>
-      <c r="H9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>183299.1</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>10.852</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="E10" s="7" t="n">
+        <v>10.949</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>6647036.36</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="F11" s="8" t="n">
         <v>6647036.36</v>
       </c>
     </row>
